--- a/OMOP Analysis/Results/Overall/overall_combined_summary_costs_OMOP.xlsx
+++ b/OMOP Analysis/Results/Overall/overall_combined_summary_costs_OMOP.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -426,154 +426,74 @@
         <v>22900</v>
       </c>
       <c r="C2">
-        <v>793.01</v>
+        <v>1087.13</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>13132.31</v>
+        <v>19809.38</v>
       </c>
       <c r="F2">
-        <v>792.59</v>
+        <v>1116.37</v>
       </c>
       <c r="G2">
-        <v>563.61</v>
+        <v>763.51</v>
       </c>
       <c r="H2">
-        <v>248.25</v>
+        <v>331.22</v>
       </c>
       <c r="I2">
-        <v>1069.41</v>
+        <v>1470.56</v>
       </c>
       <c r="J2">
-        <v>5.24</v>
+        <v>7.38</v>
       </c>
       <c r="K2">
-        <v>782.74</v>
+        <v>1072.67</v>
       </c>
       <c r="L2">
-        <v>803.28</v>
+        <v>1101.59</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>All Patients &amp; relevant encounters</t>
+          <t>Users &amp; all encounters</t>
         </is>
       </c>
       <c r="B3">
-        <v>22900</v>
+        <v>22302</v>
       </c>
       <c r="C3">
-        <v>689.47</v>
+        <v>1115.95</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="E3">
-        <v>12421.25</v>
+        <v>19809.38</v>
       </c>
       <c r="F3">
-        <v>719.4</v>
+        <v>1117.09</v>
       </c>
       <c r="G3">
-        <v>481</v>
+        <v>791.42</v>
       </c>
       <c r="H3">
-        <v>201</v>
+        <v>358.06</v>
       </c>
       <c r="I3">
-        <v>932.01</v>
+        <v>1494.93</v>
       </c>
       <c r="J3">
-        <v>4.75</v>
+        <v>7.48</v>
       </c>
       <c r="K3">
-        <v>680.15</v>
+        <v>1101.29</v>
       </c>
       <c r="L3">
-        <v>698.79</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Users &amp; all encounters</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>22218</v>
-      </c>
-      <c r="C4">
-        <v>816.5599999999999</v>
-      </c>
-      <c r="D4">
-        <v>2.22</v>
-      </c>
-      <c r="E4">
-        <v>13132.31</v>
-      </c>
-      <c r="F4">
-        <v>792.95</v>
-      </c>
-      <c r="G4">
-        <v>586.75</v>
-      </c>
-      <c r="H4">
-        <v>272.47</v>
-      </c>
-      <c r="I4">
-        <v>1092.07</v>
-      </c>
-      <c r="J4">
-        <v>5.32</v>
-      </c>
-      <c r="K4">
-        <v>806.14</v>
-      </c>
-      <c r="L4">
-        <v>826.99</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Users &amp; relevant encounters</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>22218</v>
-      </c>
-      <c r="C5">
-        <v>710.63</v>
-      </c>
-      <c r="D5">
-        <v>0.95</v>
-      </c>
-      <c r="E5">
-        <v>12421.25</v>
-      </c>
-      <c r="F5">
-        <v>719.99</v>
-      </c>
-      <c r="G5">
-        <v>497.54</v>
-      </c>
-      <c r="H5">
-        <v>222</v>
-      </c>
-      <c r="I5">
-        <v>954.03</v>
-      </c>
-      <c r="J5">
-        <v>4.83</v>
-      </c>
-      <c r="K5">
-        <v>701.17</v>
-      </c>
-      <c r="L5">
-        <v>720.1</v>
+        <v>1130.61</v>
       </c>
     </row>
   </sheetData>
